--- a/experiment/DAT_bestx4/Test/results-Urban100/Urban100.xlsx
+++ b/experiment/DAT_bestx4/Test/results-Urban100/Urban100.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27.57</v>
+        <v>27.62</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7657</v>
+        <v>0.7667</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26.67</v>
+        <v>26.72</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8128</v>
+        <v>0.8149</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23.94</v>
+        <v>23.98</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6897</v>
+        <v>0.6921</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.18</v>
+        <v>23.2</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8326</v>
+        <v>0.834</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28.09</v>
+        <v>28.21</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9491000000000001</v>
+        <v>0.9506</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22.49</v>
+        <v>22.51</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6259</v>
+        <v>0.627</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>29.52</v>
+        <v>29.55</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8615</v>
+        <v>0.8622</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21.57</v>
+        <v>21.62</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6636</v>
+        <v>0.6674</v>
       </c>
     </row>
     <row r="10">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>34.14</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9271</v>
+        <v>0.9288</v>
       </c>
     </row>
     <row r="11">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>27.25</v>
+        <v>27.36</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8883</v>
+        <v>0.8903</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17.8</v>
+        <v>17.86</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7858000000000001</v>
+        <v>0.7906</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>23.95</v>
+        <v>23.97</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7359</v>
+        <v>0.738</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>29.56</v>
+        <v>29.62</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8385</v>
+        <v>0.8401</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22.42</v>
+        <v>22.44</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6865</v>
+        <v>0.6884</v>
       </c>
     </row>
     <row r="16">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>26.08</v>
+        <v>26.15</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7347</v>
+        <v>0.7367</v>
       </c>
     </row>
     <row r="17">
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>30.48</v>
+        <v>30.61</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9151</v>
+        <v>0.9162</v>
       </c>
     </row>
     <row r="18">
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>25.83</v>
+        <v>25.89</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8293</v>
+        <v>0.8316</v>
       </c>
     </row>
     <row r="19">
@@ -673,10 +673,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>26.4</v>
+        <v>26.39</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7167</v>
+        <v>0.7169</v>
       </c>
     </row>
     <row r="20">
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>22.21</v>
+        <v>22.32</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8131</v>
+        <v>0.8161</v>
       </c>
     </row>
     <row r="21">
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>22.2</v>
+        <v>22.24</v>
       </c>
       <c r="C21" t="n">
-        <v>0.72</v>
+        <v>0.722</v>
       </c>
     </row>
     <row r="22">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>29.75</v>
+        <v>29.82</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7861</v>
+        <v>0.7874</v>
       </c>
     </row>
     <row r="23">
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>26.14</v>
+        <v>26.16</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7627</v>
+        <v>0.7637</v>
       </c>
     </row>
     <row r="24">
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>30.48</v>
+        <v>30.55</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9161</v>
+        <v>0.917</v>
       </c>
     </row>
     <row r="25">
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>20.58</v>
+        <v>20.57</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6739000000000001</v>
+        <v>0.6768</v>
       </c>
     </row>
     <row r="26">
@@ -764,10 +764,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>31.58</v>
+        <v>31.66</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8963</v>
+        <v>0.8976</v>
       </c>
     </row>
     <row r="27">
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>28</v>
+        <v>28.05</v>
       </c>
       <c r="C27" t="n">
-        <v>0.7006</v>
+        <v>0.703</v>
       </c>
     </row>
     <row r="28">
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>28.39</v>
+        <v>28.43</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7983</v>
+        <v>0.7997</v>
       </c>
     </row>
     <row r="29">
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>31.49</v>
+        <v>31.53</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.8784</v>
       </c>
     </row>
     <row r="30">
@@ -819,7 +819,7 @@
         <v>27.13</v>
       </c>
       <c r="C30" t="n">
-        <v>0.867</v>
+        <v>0.8685</v>
       </c>
     </row>
     <row r="31">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>24.8</v>
+        <v>24.85</v>
       </c>
       <c r="C31" t="n">
-        <v>0.8148</v>
+        <v>0.8172</v>
       </c>
     </row>
     <row r="32">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>24.35</v>
+        <v>24.37</v>
       </c>
       <c r="C32" t="n">
-        <v>0.7929</v>
+        <v>0.7939000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>29.19</v>
+        <v>29.28</v>
       </c>
       <c r="C33" t="n">
-        <v>0.8574000000000001</v>
+        <v>0.8594000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>27.19</v>
+        <v>27.31</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8038999999999999</v>
+        <v>0.8090000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -881,10 +881,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>23.12</v>
+        <v>23.16</v>
       </c>
       <c r="C35" t="n">
-        <v>0.5888</v>
+        <v>0.5904</v>
       </c>
     </row>
     <row r="36">
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>28.83</v>
+        <v>28.9</v>
       </c>
       <c r="C36" t="n">
-        <v>0.8695000000000001</v>
+        <v>0.8718</v>
       </c>
     </row>
     <row r="37">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>28.87</v>
+        <v>28.95</v>
       </c>
       <c r="C37" t="n">
-        <v>0.8836000000000001</v>
+        <v>0.8849</v>
       </c>
     </row>
     <row r="38">
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>26.61</v>
+        <v>26.64</v>
       </c>
       <c r="C38" t="n">
-        <v>0.8027</v>
+        <v>0.8038</v>
       </c>
     </row>
     <row r="39">
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>27.17</v>
+        <v>27.22</v>
       </c>
       <c r="C39" t="n">
-        <v>0.6873</v>
+        <v>0.6899</v>
       </c>
     </row>
     <row r="40">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>23.06</v>
+        <v>23.12</v>
       </c>
       <c r="C40" t="n">
-        <v>0.745</v>
+        <v>0.7484</v>
       </c>
     </row>
     <row r="41">
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>27.11</v>
+        <v>27.15</v>
       </c>
       <c r="C41" t="n">
-        <v>0.9371</v>
+        <v>0.9386</v>
       </c>
     </row>
     <row r="42">
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>26.44</v>
+        <v>26.55</v>
       </c>
       <c r="C42" t="n">
-        <v>0.8812</v>
+        <v>0.8833</v>
       </c>
     </row>
     <row r="43">
@@ -988,7 +988,7 @@
         <v>28.78</v>
       </c>
       <c r="C43" t="n">
-        <v>0.8819</v>
+        <v>0.8821</v>
       </c>
     </row>
     <row r="44">
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>31.73</v>
+        <v>31.94</v>
       </c>
       <c r="C44" t="n">
-        <v>0.9308</v>
+        <v>0.9319</v>
       </c>
     </row>
     <row r="45">
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>32.09</v>
+        <v>32.19</v>
       </c>
       <c r="C45" t="n">
-        <v>0.8691</v>
+        <v>0.872</v>
       </c>
     </row>
     <row r="46">
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>23.39</v>
+        <v>23.21</v>
       </c>
       <c r="C46" t="n">
-        <v>0.6971000000000001</v>
+        <v>0.6887</v>
       </c>
     </row>
     <row r="47">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>23.76</v>
+        <v>23.81</v>
       </c>
       <c r="C47" t="n">
-        <v>0.7637</v>
+        <v>0.7665999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>22.15</v>
+        <v>22.2</v>
       </c>
       <c r="C48" t="n">
-        <v>0.7782</v>
+        <v>0.7812</v>
       </c>
     </row>
     <row r="49">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>20.56</v>
+        <v>20.62</v>
       </c>
       <c r="C49" t="n">
-        <v>0.8198</v>
+        <v>0.8222</v>
       </c>
     </row>
     <row r="50">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>23.6</v>
+        <v>23.66</v>
       </c>
       <c r="C50" t="n">
-        <v>0.7532</v>
+        <v>0.7554999999999999</v>
       </c>
     </row>
     <row r="51">
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>25.44</v>
+        <v>25.46</v>
       </c>
       <c r="C51" t="n">
-        <v>0.7748</v>
+        <v>0.7766</v>
       </c>
     </row>
     <row r="52">
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>27.53</v>
+        <v>27.56</v>
       </c>
       <c r="C52" t="n">
-        <v>0.8488</v>
+        <v>0.8499</v>
       </c>
     </row>
     <row r="53">
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>28.65</v>
+        <v>28.72</v>
       </c>
       <c r="C53" t="n">
-        <v>0.902</v>
+        <v>0.9034</v>
       </c>
     </row>
     <row r="54">
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>22.43</v>
+        <v>22.47</v>
       </c>
       <c r="C54" t="n">
-        <v>0.7299</v>
+        <v>0.7324000000000001</v>
       </c>
     </row>
     <row r="55">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>21.28</v>
+        <v>21.31</v>
       </c>
       <c r="C55" t="n">
-        <v>0.6536999999999999</v>
+        <v>0.6556</v>
       </c>
     </row>
     <row r="56">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>32.86</v>
+        <v>33.08</v>
       </c>
       <c r="C56" t="n">
-        <v>0.9433</v>
+        <v>0.9447</v>
       </c>
     </row>
     <row r="57">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>25.08</v>
+        <v>25.12</v>
       </c>
       <c r="C57" t="n">
-        <v>0.7846</v>
+        <v>0.7867</v>
       </c>
     </row>
     <row r="58">
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>30.94</v>
+        <v>31.02</v>
       </c>
       <c r="C58" t="n">
-        <v>0.8923</v>
+        <v>0.8939</v>
       </c>
     </row>
     <row r="59">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>26.01</v>
+        <v>26.05</v>
       </c>
       <c r="C59" t="n">
-        <v>0.8612</v>
+        <v>0.8626</v>
       </c>
     </row>
     <row r="60">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>22.24</v>
+        <v>22.31</v>
       </c>
       <c r="C60" t="n">
-        <v>0.7665</v>
+        <v>0.7689</v>
       </c>
     </row>
     <row r="61">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>22.63</v>
+        <v>22.65</v>
       </c>
       <c r="C61" t="n">
-        <v>0.5724</v>
+        <v>0.5745</v>
       </c>
     </row>
     <row r="62">
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>24.85</v>
+        <v>24.87</v>
       </c>
       <c r="C62" t="n">
-        <v>0.7602</v>
+        <v>0.7625</v>
       </c>
     </row>
     <row r="63">
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>22.07</v>
+        <v>22.23</v>
       </c>
       <c r="C63" t="n">
-        <v>0.8151</v>
+        <v>0.8207</v>
       </c>
     </row>
     <row r="64">
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>22.34</v>
+        <v>22.36</v>
       </c>
       <c r="C64" t="n">
-        <v>0.6162</v>
+        <v>0.6173999999999999</v>
       </c>
     </row>
     <row r="65">
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>26.74</v>
+        <v>26.78</v>
       </c>
       <c r="C65" t="n">
-        <v>0.7885</v>
+        <v>0.7897</v>
       </c>
     </row>
     <row r="66">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>25.49</v>
+        <v>25.52</v>
       </c>
       <c r="C66" t="n">
-        <v>0.7257</v>
+        <v>0.7279</v>
       </c>
     </row>
     <row r="67">
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>20.3</v>
+        <v>20.39</v>
       </c>
       <c r="C68" t="n">
-        <v>0.8829</v>
+        <v>0.8849</v>
       </c>
     </row>
     <row r="69">
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>30.25</v>
+        <v>30.31</v>
       </c>
       <c r="C69" t="n">
-        <v>0.8808</v>
+        <v>0.8828</v>
       </c>
     </row>
     <row r="70">
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>24.85</v>
+        <v>24.87</v>
       </c>
       <c r="C70" t="n">
-        <v>0.7541</v>
+        <v>0.755</v>
       </c>
     </row>
     <row r="71">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>22.2</v>
+        <v>22.22</v>
       </c>
       <c r="C71" t="n">
-        <v>0.5982</v>
+        <v>0.5992</v>
       </c>
     </row>
     <row r="72">
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>28.06</v>
+        <v>28.12</v>
       </c>
       <c r="C72" t="n">
-        <v>0.6699000000000001</v>
+        <v>0.6716</v>
       </c>
     </row>
     <row r="73">
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>20.2</v>
+        <v>20.25</v>
       </c>
       <c r="C73" t="n">
-        <v>0.8152</v>
+        <v>0.8177</v>
       </c>
     </row>
     <row r="74">
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>20.33</v>
+        <v>20.38</v>
       </c>
       <c r="C74" t="n">
-        <v>0.5778</v>
+        <v>0.5832000000000001</v>
       </c>
     </row>
     <row r="75">
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>23.79</v>
+        <v>23.9</v>
       </c>
       <c r="C75" t="n">
-        <v>0.7075</v>
+        <v>0.7155</v>
       </c>
     </row>
     <row r="76">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>31.53</v>
+        <v>31.63</v>
       </c>
       <c r="C76" t="n">
-        <v>0.8821</v>
+        <v>0.8832</v>
       </c>
     </row>
     <row r="77">
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>22.99</v>
+        <v>23.13</v>
       </c>
       <c r="C77" t="n">
-        <v>0.731</v>
+        <v>0.7391</v>
       </c>
     </row>
     <row r="78">
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>22.78</v>
+        <v>22.79</v>
       </c>
       <c r="C78" t="n">
-        <v>0.6772</v>
+        <v>0.6784</v>
       </c>
     </row>
     <row r="79">
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>27.43</v>
+        <v>27.51</v>
       </c>
       <c r="C79" t="n">
-        <v>0.7723</v>
+        <v>0.7747000000000001</v>
       </c>
     </row>
     <row r="80">
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>25.46</v>
+        <v>25.49</v>
       </c>
       <c r="C80" t="n">
-        <v>0.697</v>
+        <v>0.6984</v>
       </c>
     </row>
     <row r="81">
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>35.73</v>
+        <v>35.8</v>
       </c>
       <c r="C81" t="n">
-        <v>0.9528</v>
+        <v>0.9534</v>
       </c>
     </row>
     <row r="82">
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>37</v>
+        <v>37.23</v>
       </c>
       <c r="C82" t="n">
-        <v>0.9693000000000001</v>
+        <v>0.9701</v>
       </c>
     </row>
     <row r="83">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>32.8</v>
+        <v>32.89</v>
       </c>
       <c r="C83" t="n">
-        <v>0.9404</v>
+        <v>0.9408</v>
       </c>
     </row>
     <row r="84">
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>22.36</v>
+        <v>22.39</v>
       </c>
       <c r="C84" t="n">
-        <v>0.7016</v>
+        <v>0.7043</v>
       </c>
     </row>
     <row r="85">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>28.73</v>
+        <v>28.77</v>
       </c>
       <c r="C85" t="n">
-        <v>0.8117</v>
+        <v>0.8129</v>
       </c>
     </row>
     <row r="86">
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>28.5</v>
+        <v>28.56</v>
       </c>
       <c r="C86" t="n">
-        <v>0.9042</v>
+        <v>0.9056</v>
       </c>
     </row>
     <row r="87">
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>30.51</v>
+        <v>30.57</v>
       </c>
       <c r="C87" t="n">
-        <v>0.8856000000000001</v>
+        <v>0.8866000000000001</v>
       </c>
     </row>
     <row r="88">
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>27.85</v>
+        <v>27.9</v>
       </c>
       <c r="C88" t="n">
-        <v>0.8844</v>
+        <v>0.8861</v>
       </c>
     </row>
     <row r="89">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>19.98</v>
+        <v>19.99</v>
       </c>
       <c r="C89" t="n">
-        <v>0.5726</v>
+        <v>0.5742</v>
       </c>
     </row>
     <row r="90">
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>26.8</v>
+        <v>26.82</v>
       </c>
       <c r="C90" t="n">
-        <v>0.7174</v>
+        <v>0.7189</v>
       </c>
     </row>
     <row r="91">
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>38.08</v>
+        <v>38.17</v>
       </c>
       <c r="C91" t="n">
-        <v>0.9748</v>
+        <v>0.9752999999999999</v>
       </c>
     </row>
     <row r="92">
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>24.03</v>
+        <v>24.07</v>
       </c>
       <c r="C92" t="n">
-        <v>0.6834</v>
+        <v>0.6854</v>
       </c>
     </row>
     <row r="93">
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>18.92</v>
+        <v>18.91</v>
       </c>
       <c r="C93" t="n">
-        <v>0.6516</v>
+        <v>0.6518</v>
       </c>
     </row>
     <row r="94">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>28.98</v>
+        <v>28.8</v>
       </c>
       <c r="C94" t="n">
-        <v>0.9231</v>
+        <v>0.9225</v>
       </c>
     </row>
     <row r="95">
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>27.19</v>
+        <v>27.23</v>
       </c>
       <c r="C95" t="n">
-        <v>0.7841</v>
+        <v>0.7856</v>
       </c>
     </row>
     <row r="96">
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>20.16</v>
+        <v>20.2</v>
       </c>
       <c r="C96" t="n">
-        <v>0.4427</v>
+        <v>0.4474</v>
       </c>
     </row>
     <row r="97">
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>25.63</v>
+        <v>25.6</v>
       </c>
       <c r="C97" t="n">
-        <v>0.8711</v>
+        <v>0.8714</v>
       </c>
     </row>
     <row r="98">
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>24.91</v>
+        <v>24.96</v>
       </c>
       <c r="C98" t="n">
-        <v>0.7634</v>
+        <v>0.766</v>
       </c>
     </row>
     <row r="99">
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>20.76</v>
+        <v>20.79</v>
       </c>
       <c r="C99" t="n">
-        <v>0.5342</v>
+        <v>0.538</v>
       </c>
     </row>
     <row r="100">
@@ -1729,7 +1729,7 @@
         <v>25.82</v>
       </c>
       <c r="C100" t="n">
-        <v>0.7911</v>
+        <v>0.7954</v>
       </c>
     </row>
     <row r="101">
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>26.03</v>
+        <v>26.09</v>
       </c>
       <c r="C101" t="n">
-        <v>0.7387</v>
+        <v>0.7409</v>
       </c>
     </row>
     <row r="102">
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>26.07</v>
+        <v>26.13</v>
       </c>
       <c r="C102" t="n">
-        <v>0.7845</v>
+        <v>0.7864</v>
       </c>
     </row>
   </sheetData>
